--- a/tame_output/ON/bt/strategyON_20240301.xlsx
+++ b/tame_output/ON/bt/strategyON_20240301.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-53.3%</t>
+          <t>-53.2%</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>128.0%</t>
+          <t>128.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.7%</t>
         </is>
       </c>
     </row>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191743</v>
+        <v>3.302618194191742</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108645</v>
+        <v>3.305023265108644</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097826</v>
+        <v>3.341378723097825</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094122</v>
+        <v>3.374439043094121</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199292</v>
+        <v>3.40596051119929</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.4246333549696</v>
+        <v>3.424633354969599</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923093</v>
+        <v>3.419979433923092</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297755</v>
+        <v>3.458100091297754</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317621</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880267</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234392</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792539</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410714</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.357451081463714</v>
+        <v>3.357451081463715</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>1.083047936800387</v>
+        <v>1.084042909396122</v>
       </c>
       <c r="E1889" t="n">
-        <v>3.599134311163404</v>
+        <v>3.599532300201698</v>
       </c>
       <c r="F1889" t="n">
-        <v>2.333266866468279</v>
+        <v>2.334382843979515</v>
       </c>
       <c r="G1889" t="n">
-        <v>4.566231680637963</v>
+        <v>4.566901267144705</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240301.xlsx
+++ b/tame_output/ON/bt/strategyON_20240301.xlsx
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>415.9%</t>
+          <t>415.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-53.2%</t>
+          <t>-52.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>85.9%</t>
+          <t>86.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.7%</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>122.5%</t>
+          <t>122.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.8%</t>
         </is>
       </c>
     </row>
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>1.084042909396122</v>
+        <v>1.087226859149587</v>
       </c>
       <c r="E1889" t="n">
-        <v>3.599532300201698</v>
+        <v>3.600805880103084</v>
       </c>
       <c r="F1889" t="n">
-        <v>2.334382843979515</v>
+        <v>2.337363094426717</v>
       </c>
       <c r="G1889" t="n">
-        <v>4.566901267144705</v>
+        <v>4.568689417413026</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240301.xlsx
+++ b/tame_output/ON/bt/strategyON_20240301.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>4.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>87.1%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-145.4%</t>
+          <t>-178.1%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-10.5%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,32 +1007,32 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>415.8%</t>
+          <t>427.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-23.6%</t>
+          <t>-35.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-52.8%</t>
+          <t>-85.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>84.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-58.6%</t>
+          <t>-71.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>81.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-29.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-59.3%</t>
+          <t>-92.0%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.1%</t>
+          <t>-156.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>-22.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>128.1%</t>
+          <t>118.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-36.0%</t>
+          <t>-55.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>122.6%</t>
+          <t>113.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>-8.7%</t>
         </is>
       </c>
     </row>
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>0.1612741448978827</v>
+        <v>-0.1658425387304278</v>
       </c>
       <c r="E1851" t="n">
-        <v>3.174157800393719</v>
+        <v>3.043311126942395</v>
       </c>
       <c r="F1851" t="n">
-        <v>1.646929810264191</v>
+        <v>1.319813126635881</v>
       </c>
       <c r="G1851" t="n">
-        <v>4.098162452906829</v>
+        <v>3.901892442729842</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>0.1683463286043321</v>
+        <v>-0.1587703550239783</v>
       </c>
       <c r="E1852" t="n">
-        <v>3.197324963615067</v>
+        <v>3.066478290163743</v>
       </c>
       <c r="F1852" t="n">
-        <v>1.654001993970641</v>
+        <v>1.32688531034233</v>
       </c>
       <c r="G1852" t="n">
-        <v>4.122744052869467</v>
+        <v>3.92647404269248</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>0.1716830751133038</v>
+        <v>-0.1554336085150066</v>
       </c>
       <c r="E1853" t="n">
-        <v>3.206758412627225</v>
+        <v>3.075911739175901</v>
       </c>
       <c r="F1853" t="n">
-        <v>1.656694026389672</v>
+        <v>1.329577342761362</v>
       </c>
       <c r="G1853" t="n">
-        <v>4.132458022729454</v>
+        <v>3.936188012552468</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>0.1702304086501945</v>
+        <v>-0.1568862749781159</v>
       </c>
       <c r="E1854" t="n">
-        <v>3.207283738085713</v>
+        <v>3.076437064634389</v>
       </c>
       <c r="F1854" t="n">
-        <v>1.655241359926563</v>
+        <v>1.328124676298252</v>
       </c>
       <c r="G1854" t="n">
-        <v>4.132692814895321</v>
+        <v>3.936422804718334</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>0.1697997096015991</v>
+        <v>-0.1573169740267114</v>
       </c>
       <c r="E1855" t="n">
-        <v>3.205653997279138</v>
+        <v>3.074807323827814</v>
       </c>
       <c r="F1855" t="n">
-        <v>1.655241359926563</v>
+        <v>1.328124676298252</v>
       </c>
       <c r="G1855" t="n">
-        <v>4.131235353708184</v>
+        <v>3.934965343531197</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>0.1689625326197639</v>
+        <v>-0.1581541510085465</v>
       </c>
       <c r="E1856" t="n">
-        <v>3.20708824994102</v>
+        <v>3.076241576489696</v>
       </c>
       <c r="F1856" t="n">
-        <v>1.654287108664692</v>
+        <v>1.327170425036381</v>
       </c>
       <c r="G1856" t="n">
-        <v>4.132431926405677</v>
+        <v>3.936161916228691</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>0.1574580476214788</v>
+        <v>-0.1696586360068316</v>
       </c>
       <c r="E1857" t="n">
-        <v>3.198592514597964</v>
+        <v>3.06774584114664</v>
       </c>
       <c r="F1857" t="n">
-        <v>1.642782623666406</v>
+        <v>1.315665940038096</v>
       </c>
       <c r="G1857" t="n">
-        <v>4.121635294062964</v>
+        <v>3.925365283885978</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>0.150797107399331</v>
+        <v>-0.1763195762289794</v>
       </c>
       <c r="E1858" t="n">
-        <v>3.197701065209364</v>
+        <v>3.06685439175804</v>
       </c>
       <c r="F1858" t="n">
-        <v>1.642782623666406</v>
+        <v>1.315665940038096</v>
       </c>
       <c r="G1858" t="n">
-        <v>4.123408220763223</v>
+        <v>3.927138210586238</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>0.1486465876191197</v>
+        <v>-0.1784700960091907</v>
       </c>
       <c r="E1859" t="n">
-        <v>3.183173744764685</v>
+        <v>3.05232707131336</v>
       </c>
       <c r="F1859" t="n">
-        <v>1.641134615827808</v>
+        <v>1.314017932199498</v>
       </c>
       <c r="G1859" t="n">
-        <v>4.108752303527469</v>
+        <v>3.912482293350482</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>0.1617088419680874</v>
+        <v>-0.165407841660223</v>
       </c>
       <c r="E1860" t="n">
-        <v>3.176683421506362</v>
+        <v>3.045836748055038</v>
       </c>
       <c r="F1860" t="n">
-        <v>1.646969162617875</v>
+        <v>1.319852478989564</v>
       </c>
       <c r="G1860" t="n">
-        <v>4.1005378066036</v>
+        <v>3.904267796426613</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>0.1601446908577843</v>
+        <v>-0.1669719927705261</v>
       </c>
       <c r="E1861" t="n">
-        <v>3.174638352718206</v>
+        <v>3.043791679266882</v>
       </c>
       <c r="F1861" t="n">
-        <v>1.646969162617875</v>
+        <v>1.319852478989564</v>
       </c>
       <c r="G1861" t="n">
-        <v>4.099118398259565</v>
+        <v>3.902848388082579</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>0.1621932757194949</v>
+        <v>-0.1649234079088155</v>
       </c>
       <c r="E1862" t="n">
-        <v>3.181945346897132</v>
+        <v>3.051098673445808</v>
       </c>
       <c r="F1862" t="n">
-        <v>1.649216862676067</v>
+        <v>1.322100179047757</v>
       </c>
       <c r="G1862" t="n">
-        <v>4.106954578528722</v>
+        <v>3.910684568351735</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>0.1646203402482132</v>
+        <v>-0.1624963433800972</v>
       </c>
       <c r="E1863" t="n">
-        <v>3.18217068771445</v>
+        <v>3.051324014263126</v>
       </c>
       <c r="F1863" t="n">
-        <v>1.648884080868916</v>
+        <v>1.321767397240605</v>
       </c>
       <c r="G1863" t="n">
-        <v>4.106009424450262</v>
+        <v>3.909739414273276</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>0.1633283184738751</v>
+        <v>-0.1637883651544353</v>
       </c>
       <c r="E1864" t="n">
-        <v>3.180415423019475</v>
+        <v>3.04956874956815</v>
       </c>
       <c r="F1864" t="n">
-        <v>1.647592059094578</v>
+        <v>1.320475375466267</v>
       </c>
       <c r="G1864" t="n">
-        <v>4.103995755400419</v>
+        <v>3.907725745223432</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>0.1585137262190337</v>
+        <v>-0.1686029574092767</v>
       </c>
       <c r="E1865" t="n">
-        <v>3.173675018588999</v>
+        <v>3.042828345137675</v>
       </c>
       <c r="F1865" t="n">
-        <v>1.647592059094578</v>
+        <v>1.320475375466267</v>
       </c>
       <c r="G1865" t="n">
-        <v>4.09918118787188</v>
+        <v>3.902911177694893</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>0.1616704272492376</v>
+        <v>-0.1654462563790728</v>
       </c>
       <c r="E1866" t="n">
-        <v>3.172931749609957</v>
+        <v>3.042085076158633</v>
       </c>
       <c r="F1866" t="n">
-        <v>1.647592059094578</v>
+        <v>1.320475375466267</v>
       </c>
       <c r="G1866" t="n">
-        <v>4.097175238480757</v>
+        <v>3.90090522830377</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>0.1576573948367158</v>
+        <v>-0.1694592887915946</v>
       </c>
       <c r="E1867" t="n">
-        <v>3.181585227313628</v>
+        <v>3.050738553862304</v>
       </c>
       <c r="F1867" t="n">
-        <v>1.647592059094578</v>
+        <v>1.320475375466267</v>
       </c>
       <c r="G1867" t="n">
-        <v>4.107433929149435</v>
+        <v>3.911163918972449</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>0.1439425305116043</v>
+        <v>-0.1831741531167062</v>
       </c>
       <c r="E1868" t="n">
-        <v>3.172198846729278</v>
+        <v>3.041352173277954</v>
       </c>
       <c r="F1868" t="n">
-        <v>1.647592059094578</v>
+        <v>1.320475375466267</v>
       </c>
       <c r="G1868" t="n">
-        <v>4.103533494295131</v>
+        <v>3.907263484118144</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>0.1384256106676379</v>
+        <v>-0.1886910729606726</v>
       </c>
       <c r="E1869" t="n">
-        <v>3.168396998846692</v>
+        <v>3.037550325395368</v>
       </c>
       <c r="F1869" t="n">
-        <v>1.647592059094578</v>
+        <v>1.320475375466267</v>
       </c>
       <c r="G1869" t="n">
-        <v>4.101938414350132</v>
+        <v>3.905668404173145</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>0.1336125722023011</v>
+        <v>-0.1935041114260093</v>
       </c>
       <c r="E1870" t="n">
-        <v>3.170250759389766</v>
+        <v>3.039404085938442</v>
       </c>
       <c r="F1870" t="n">
-        <v>1.646045424391792</v>
+        <v>1.318928740763481</v>
       </c>
       <c r="G1870" t="n">
-        <v>4.104789409457668</v>
+        <v>3.908519399280682</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>0.135729730926594</v>
+        <v>-0.1913869527017165</v>
       </c>
       <c r="E1871" t="n">
-        <v>3.16707131834508</v>
+        <v>3.036224644893756</v>
       </c>
       <c r="F1871" t="n">
-        <v>1.646045424391792</v>
+        <v>1.318928740763481</v>
       </c>
       <c r="G1871" t="n">
-        <v>4.100763104923265</v>
+        <v>3.904493094746279</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>0.1362070775050837</v>
+        <v>-0.1909096061232267</v>
       </c>
       <c r="E1872" t="n">
-        <v>3.167160155654892</v>
+        <v>3.036313482203568</v>
       </c>
       <c r="F1872" t="n">
-        <v>1.646045424391792</v>
+        <v>1.318928740763481</v>
       </c>
       <c r="G1872" t="n">
-        <v>4.100661003601681</v>
+        <v>3.904390993424695</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>0.1372318638119413</v>
+        <v>-0.1898848198163691</v>
       </c>
       <c r="E1873" t="n">
-        <v>3.170141586149065</v>
+        <v>3.039294912697741</v>
       </c>
       <c r="F1873" t="n">
-        <v>1.647070210698649</v>
+        <v>1.319953527070339</v>
       </c>
       <c r="G1873" t="n">
-        <v>4.103847391357226</v>
+        <v>3.907577381180239</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>0.1184904835530226</v>
+        <v>-0.2086262000752878</v>
       </c>
       <c r="E1874" t="n">
-        <v>3.167995337343548</v>
+        <v>3.037148663892224</v>
       </c>
       <c r="F1874" t="n">
-        <v>1.647070210698649</v>
+        <v>1.319953527070339</v>
       </c>
       <c r="G1874" t="n">
-        <v>4.109197694655276</v>
+        <v>3.91292768447829</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>0.1055211407679241</v>
+        <v>-0.2215955428603864</v>
       </c>
       <c r="E1875" t="n">
-        <v>3.170723620186686</v>
+        <v>3.039876946735362</v>
       </c>
       <c r="F1875" t="n">
-        <v>1.634100867913551</v>
+        <v>1.30698418428524</v>
       </c>
       <c r="G1875" t="n">
-        <v>4.109332108941395</v>
+        <v>3.913062098764408</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>0.1119972875614836</v>
+        <v>-0.2151193960668268</v>
       </c>
       <c r="E1876" t="n">
-        <v>3.176355829525879</v>
+        <v>3.045509156074555</v>
       </c>
       <c r="F1876" t="n">
-        <v>1.640577014707111</v>
+        <v>1.3134603310788</v>
       </c>
       <c r="G1876" t="n">
-        <v>4.116259547639299</v>
+        <v>3.919989537462313</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>0.115688212517895</v>
+        <v>-0.2114284711104155</v>
       </c>
       <c r="E1877" t="n">
-        <v>3.177832199508443</v>
+        <v>3.046985526057119</v>
       </c>
       <c r="F1877" t="n">
-        <v>1.640577014707111</v>
+        <v>1.3134603310788</v>
       </c>
       <c r="G1877" t="n">
-        <v>4.116259547639299</v>
+        <v>3.919989537462313</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>0.1229035653897107</v>
+        <v>-0.2042131182385997</v>
       </c>
       <c r="E1878" t="n">
-        <v>3.186231537775812</v>
+        <v>3.055384864324488</v>
       </c>
       <c r="F1878" t="n">
-        <v>1.710355249997492</v>
+        <v>1.383238566369182</v>
       </c>
       <c r="G1878" t="n">
-        <v>4.16363968593217</v>
+        <v>3.967369675755184</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>0.1739314114715367</v>
+        <v>-0.1531852721567737</v>
       </c>
       <c r="E1879" t="n">
-        <v>3.211125230692978</v>
+        <v>3.080278557241654</v>
       </c>
       <c r="F1879" t="n">
-        <v>1.785564588304593</v>
+        <v>1.458447904676283</v>
       </c>
       <c r="G1879" t="n">
-        <v>4.213247843400867</v>
+        <v>4.016977833223881</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>0.2474012431389851</v>
+        <v>-0.07971544048932527</v>
       </c>
       <c r="E1880" t="n">
-        <v>3.255884864853379</v>
+        <v>3.125038191402055</v>
       </c>
       <c r="F1880" t="n">
-        <v>1.859034419972042</v>
+        <v>1.531917736343731</v>
       </c>
       <c r="G1880" t="n">
-        <v>4.272701443894757</v>
+        <v>4.076431433717771</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>0.3277735986029148</v>
+        <v>0.0006569149746043501</v>
       </c>
       <c r="E1881" t="n">
-        <v>3.302589027786468</v>
+        <v>3.171742354335143</v>
       </c>
       <c r="F1881" t="n">
-        <v>1.939406775435971</v>
+        <v>1.612290091807661</v>
       </c>
       <c r="G1881" t="n">
-        <v>4.335480077920632</v>
+        <v>4.139210067743646</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>0.3607054684157656</v>
+        <v>0.03358878478745519</v>
       </c>
       <c r="E1882" t="n">
-        <v>3.308542610810012</v>
+        <v>3.177695937358687</v>
       </c>
       <c r="F1882" t="n">
-        <v>1.939406775435971</v>
+        <v>1.612290091807661</v>
       </c>
       <c r="G1882" t="n">
-        <v>4.328260913019036</v>
+        <v>4.131990902842049</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>0.3405408268662183</v>
+        <v>0.01342414323790786</v>
       </c>
       <c r="E1883" t="n">
-        <v>3.293804563416217</v>
+        <v>3.162957889964892</v>
       </c>
       <c r="F1883" t="n">
-        <v>1.919242133886424</v>
+        <v>1.592125450258113</v>
       </c>
       <c r="G1883" t="n">
-        <v>4.309489937315331</v>
+        <v>4.113219927138345</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>0.3992077568877517</v>
+        <v>0.07209107325944131</v>
       </c>
       <c r="E1884" t="n">
-        <v>3.318387125263386</v>
+        <v>3.187540451812062</v>
       </c>
       <c r="F1884" t="n">
-        <v>2.004201602316562</v>
+        <v>1.677084918688251</v>
       </c>
       <c r="G1884" t="n">
-        <v>4.36158140821197</v>
+        <v>4.165311398034984</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>0.4622769891940913</v>
+        <v>0.1351603055657808</v>
       </c>
       <c r="E1885" t="n">
-        <v>3.346308546815037</v>
+        <v>3.215461873363713</v>
       </c>
       <c r="F1885" t="n">
-        <v>1.975688039634327</v>
+        <v>1.648571356006017</v>
       </c>
       <c r="G1885" t="n">
-        <v>4.347166999231744</v>
+        <v>4.150896989054758</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>0.514292503162904</v>
+        <v>0.1871758195345936</v>
       </c>
       <c r="E1886" t="n">
-        <v>3.371105088088963</v>
+        <v>3.240258414637639</v>
       </c>
       <c r="F1886" t="n">
-        <v>1.975688039634327</v>
+        <v>1.648571356006017</v>
       </c>
       <c r="G1886" t="n">
-        <v>4.351157334918145</v>
+        <v>4.154887324741159</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>0.689862172083808</v>
+        <v>0.3627454884554975</v>
       </c>
       <c r="E1887" t="n">
-        <v>3.439857728758583</v>
+        <v>3.309011055307258</v>
       </c>
       <c r="F1887" t="n">
-        <v>1.975688039634327</v>
+        <v>1.648571356006017</v>
       </c>
       <c r="G1887" t="n">
-        <v>4.349682108019403</v>
+        <v>4.153412097842417</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>0.8871315778118061</v>
+        <v>0.5600148941834957</v>
       </c>
       <c r="E1888" t="n">
-        <v>3.533818901214654</v>
+        <v>3.40297222776333</v>
       </c>
       <c r="F1888" t="n">
-        <v>2.172957445362325</v>
+        <v>1.845840761734015</v>
       </c>
       <c r="G1888" t="n">
-        <v>4.483097161621075</v>
+        <v>4.286827151444088</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.357451081463715</v>
+        <v>3.325225350491477</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>1.087226859149587</v>
+        <v>0.7643351654251821</v>
       </c>
       <c r="E1889" t="n">
-        <v>3.600805880103084</v>
+        <v>3.471649202613321</v>
       </c>
       <c r="F1889" t="n">
-        <v>2.337363094426717</v>
+        <v>2.012297482681587</v>
       </c>
       <c r="G1889" t="n">
-        <v>4.568689417413026</v>
+        <v>4.373650050365948</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240301.xlsx
+++ b/tame_output/ON/bt/strategyON_20240301.xlsx
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,17 +949,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>87.1%</t>
+          <t>87.0%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-178.1%</t>
+          <t>-177.9%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>427.3%</t>
+          <t>428.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-35.5%</t>
+          <t>-35.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-85.1%</t>
+          <t>-85.4%</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-71.6%</t>
+          <t>-71.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-29.2%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-92.0%</t>
+          <t>-91.8%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-22.8%</t>
+          <t>-22.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>118.6%</t>
+          <t>118.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-55.6%</t>
+          <t>-55.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.6%</t>
         </is>
       </c>
     </row>
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-0.1658425387304278</v>
+        <v>-0.1633768084942244</v>
       </c>
       <c r="E1851" t="n">
-        <v>3.043311126942395</v>
+        <v>3.044297419036877</v>
       </c>
       <c r="F1851" t="n">
-        <v>1.319813126635881</v>
+        <v>1.322278856872084</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.901892442729842</v>
+        <v>3.903371880871565</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-0.1587703550239783</v>
+        <v>-0.156304624787775</v>
       </c>
       <c r="E1852" t="n">
-        <v>3.066478290163743</v>
+        <v>3.067464582258224</v>
       </c>
       <c r="F1852" t="n">
-        <v>1.32688531034233</v>
+        <v>1.329351040578534</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.92647404269248</v>
+        <v>3.927953480834202</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-0.1554336085150066</v>
+        <v>-0.1529678782788033</v>
       </c>
       <c r="E1853" t="n">
-        <v>3.075911739175901</v>
+        <v>3.076898031270382</v>
       </c>
       <c r="F1853" t="n">
-        <v>1.329577342761362</v>
+        <v>1.332043072997565</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.936188012552468</v>
+        <v>3.93766745069419</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-0.1568862749781159</v>
+        <v>-0.1544205447419126</v>
       </c>
       <c r="E1854" t="n">
-        <v>3.076437064634389</v>
+        <v>3.07742335672887</v>
       </c>
       <c r="F1854" t="n">
-        <v>1.328124676298252</v>
+        <v>1.330590406534456</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.936422804718334</v>
+        <v>3.937902242860057</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-0.1573169740267114</v>
+        <v>-0.154851243790508</v>
       </c>
       <c r="E1855" t="n">
-        <v>3.074807323827814</v>
+        <v>3.075793615922295</v>
       </c>
       <c r="F1855" t="n">
-        <v>1.328124676298252</v>
+        <v>1.330590406534456</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.934965343531197</v>
+        <v>3.93644478167292</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-0.1581541510085465</v>
+        <v>-0.1556884207723432</v>
       </c>
       <c r="E1856" t="n">
-        <v>3.076241576489696</v>
+        <v>3.077227868584178</v>
       </c>
       <c r="F1856" t="n">
-        <v>1.327170425036381</v>
+        <v>1.329636155272584</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.936161916228691</v>
+        <v>3.937641354370413</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-0.1696586360068316</v>
+        <v>-0.1671929057706283</v>
       </c>
       <c r="E1857" t="n">
-        <v>3.06774584114664</v>
+        <v>3.068732133241121</v>
       </c>
       <c r="F1857" t="n">
-        <v>1.315665940038096</v>
+        <v>1.318131670274299</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.925365283885978</v>
+        <v>3.9268447220277</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-0.1763195762289794</v>
+        <v>-0.1738538459927761</v>
       </c>
       <c r="E1858" t="n">
-        <v>3.06685439175804</v>
+        <v>3.067840683852522</v>
       </c>
       <c r="F1858" t="n">
-        <v>1.315665940038096</v>
+        <v>1.318131670274299</v>
       </c>
       <c r="G1858" t="n">
-        <v>3.927138210586238</v>
+        <v>3.928617648727959</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-0.1784700960091907</v>
+        <v>-0.1760043657729874</v>
       </c>
       <c r="E1859" t="n">
-        <v>3.05232707131336</v>
+        <v>3.053313363407842</v>
       </c>
       <c r="F1859" t="n">
-        <v>1.314017932199498</v>
+        <v>1.316483662435701</v>
       </c>
       <c r="G1859" t="n">
-        <v>3.912482293350482</v>
+        <v>3.913961731492205</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-0.165407841660223</v>
+        <v>-0.1629421114240197</v>
       </c>
       <c r="E1860" t="n">
-        <v>3.045836748055038</v>
+        <v>3.04682304014952</v>
       </c>
       <c r="F1860" t="n">
-        <v>1.319852478989564</v>
+        <v>1.322318209225768</v>
       </c>
       <c r="G1860" t="n">
-        <v>3.904267796426613</v>
+        <v>3.905747234568335</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-0.1669719927705261</v>
+        <v>-0.1645062625343228</v>
       </c>
       <c r="E1861" t="n">
-        <v>3.043791679266882</v>
+        <v>3.044777971361363</v>
       </c>
       <c r="F1861" t="n">
-        <v>1.319852478989564</v>
+        <v>1.322318209225768</v>
       </c>
       <c r="G1861" t="n">
-        <v>3.902848388082579</v>
+        <v>3.9043278262243</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-0.1649234079088155</v>
+        <v>-0.1624576776726122</v>
       </c>
       <c r="E1862" t="n">
-        <v>3.051098673445808</v>
+        <v>3.052084965540289</v>
       </c>
       <c r="F1862" t="n">
-        <v>1.322100179047757</v>
+        <v>1.32456590928396</v>
       </c>
       <c r="G1862" t="n">
-        <v>3.910684568351735</v>
+        <v>3.912164006493457</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-0.1624963433800972</v>
+        <v>-0.1600306131438939</v>
       </c>
       <c r="E1863" t="n">
-        <v>3.051324014263126</v>
+        <v>3.052310306357608</v>
       </c>
       <c r="F1863" t="n">
-        <v>1.321767397240605</v>
+        <v>1.324233127476808</v>
       </c>
       <c r="G1863" t="n">
-        <v>3.909739414273276</v>
+        <v>3.911218852414998</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-0.1637883651544353</v>
+        <v>-0.161322634918232</v>
       </c>
       <c r="E1864" t="n">
-        <v>3.04956874956815</v>
+        <v>3.050555041662632</v>
       </c>
       <c r="F1864" t="n">
-        <v>1.320475375466267</v>
+        <v>1.32294110570247</v>
       </c>
       <c r="G1864" t="n">
-        <v>3.907725745223432</v>
+        <v>3.909205183365154</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-0.1686029574092767</v>
+        <v>-0.1661372271730734</v>
       </c>
       <c r="E1865" t="n">
-        <v>3.042828345137675</v>
+        <v>3.043814637232156</v>
       </c>
       <c r="F1865" t="n">
-        <v>1.320475375466267</v>
+        <v>1.32294110570247</v>
       </c>
       <c r="G1865" t="n">
-        <v>3.902911177694893</v>
+        <v>3.904390615836615</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-0.1654462563790728</v>
+        <v>-0.1629805261428695</v>
       </c>
       <c r="E1866" t="n">
-        <v>3.042085076158633</v>
+        <v>3.043071368253115</v>
       </c>
       <c r="F1866" t="n">
-        <v>1.320475375466267</v>
+        <v>1.32294110570247</v>
       </c>
       <c r="G1866" t="n">
-        <v>3.90090522830377</v>
+        <v>3.902384666445492</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-0.1694592887915946</v>
+        <v>-0.1669935585553913</v>
       </c>
       <c r="E1867" t="n">
-        <v>3.050738553862304</v>
+        <v>3.051724845956785</v>
       </c>
       <c r="F1867" t="n">
-        <v>1.320475375466267</v>
+        <v>1.32294110570247</v>
       </c>
       <c r="G1867" t="n">
-        <v>3.911163918972449</v>
+        <v>3.912643357114171</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-0.1831741531167062</v>
+        <v>-0.1807084228805028</v>
       </c>
       <c r="E1868" t="n">
-        <v>3.041352173277954</v>
+        <v>3.042338465372436</v>
       </c>
       <c r="F1868" t="n">
-        <v>1.320475375466267</v>
+        <v>1.32294110570247</v>
       </c>
       <c r="G1868" t="n">
-        <v>3.907263484118144</v>
+        <v>3.908742922259866</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-0.1886910729606726</v>
+        <v>-0.1862253427244692</v>
       </c>
       <c r="E1869" t="n">
-        <v>3.037550325395368</v>
+        <v>3.03853661748985</v>
       </c>
       <c r="F1869" t="n">
-        <v>1.320475375466267</v>
+        <v>1.32294110570247</v>
       </c>
       <c r="G1869" t="n">
-        <v>3.905668404173145</v>
+        <v>3.907147842314867</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-0.1935041114260093</v>
+        <v>-0.191038381189806</v>
       </c>
       <c r="E1870" t="n">
-        <v>3.039404085938442</v>
+        <v>3.040390378032923</v>
       </c>
       <c r="F1870" t="n">
-        <v>1.318928740763481</v>
+        <v>1.321394470999685</v>
       </c>
       <c r="G1870" t="n">
-        <v>3.908519399280682</v>
+        <v>3.909998837422404</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-0.1913869527017165</v>
+        <v>-0.1889212224655131</v>
       </c>
       <c r="E1871" t="n">
-        <v>3.036224644893756</v>
+        <v>3.037210936988237</v>
       </c>
       <c r="F1871" t="n">
-        <v>1.318928740763481</v>
+        <v>1.321394470999685</v>
       </c>
       <c r="G1871" t="n">
-        <v>3.904493094746279</v>
+        <v>3.905972532888001</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-0.1909096061232267</v>
+        <v>-0.1884438758870234</v>
       </c>
       <c r="E1872" t="n">
-        <v>3.036313482203568</v>
+        <v>3.037299774298049</v>
       </c>
       <c r="F1872" t="n">
-        <v>1.318928740763481</v>
+        <v>1.321394470999685</v>
       </c>
       <c r="G1872" t="n">
-        <v>3.904390993424695</v>
+        <v>3.905870431566417</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-0.1898848198163691</v>
+        <v>-0.1874190895801658</v>
       </c>
       <c r="E1873" t="n">
-        <v>3.039294912697741</v>
+        <v>3.040281204792223</v>
       </c>
       <c r="F1873" t="n">
-        <v>1.319953527070339</v>
+        <v>1.322419257306542</v>
       </c>
       <c r="G1873" t="n">
-        <v>3.907577381180239</v>
+        <v>3.909056819321961</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-0.2086262000752878</v>
+        <v>-0.2061604698390845</v>
       </c>
       <c r="E1874" t="n">
-        <v>3.037148663892224</v>
+        <v>3.038134955986705</v>
       </c>
       <c r="F1874" t="n">
-        <v>1.319953527070339</v>
+        <v>1.322419257306542</v>
       </c>
       <c r="G1874" t="n">
-        <v>3.91292768447829</v>
+        <v>3.914407122620012</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-0.2215955428603864</v>
+        <v>-0.219129812624183</v>
       </c>
       <c r="E1875" t="n">
-        <v>3.039876946735362</v>
+        <v>3.040863238829843</v>
       </c>
       <c r="F1875" t="n">
-        <v>1.30698418428524</v>
+        <v>1.309449914521444</v>
       </c>
       <c r="G1875" t="n">
-        <v>3.913062098764408</v>
+        <v>3.91454153690613</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-0.2151193960668268</v>
+        <v>-0.2126536658306235</v>
       </c>
       <c r="E1876" t="n">
-        <v>3.045509156074555</v>
+        <v>3.046495448169036</v>
       </c>
       <c r="F1876" t="n">
-        <v>1.3134603310788</v>
+        <v>1.315926061315003</v>
       </c>
       <c r="G1876" t="n">
-        <v>3.919989537462313</v>
+        <v>3.921468975604035</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-0.2114284711104155</v>
+        <v>-0.2089627408742121</v>
       </c>
       <c r="E1877" t="n">
-        <v>3.046985526057119</v>
+        <v>3.0479718181516</v>
       </c>
       <c r="F1877" t="n">
-        <v>1.3134603310788</v>
+        <v>1.315926061315003</v>
       </c>
       <c r="G1877" t="n">
-        <v>3.919989537462313</v>
+        <v>3.921468975604035</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-0.2042131182385997</v>
+        <v>-0.2017473880023964</v>
       </c>
       <c r="E1878" t="n">
-        <v>3.055384864324488</v>
+        <v>3.056371156418969</v>
       </c>
       <c r="F1878" t="n">
-        <v>1.383238566369182</v>
+        <v>1.385704296605385</v>
       </c>
       <c r="G1878" t="n">
-        <v>3.967369675755184</v>
+        <v>3.968849113896907</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-0.1531852721567737</v>
+        <v>-0.1507195419205704</v>
       </c>
       <c r="E1879" t="n">
-        <v>3.080278557241654</v>
+        <v>3.081264849336136</v>
       </c>
       <c r="F1879" t="n">
-        <v>1.458447904676283</v>
+        <v>1.460913634912486</v>
       </c>
       <c r="G1879" t="n">
-        <v>4.016977833223881</v>
+        <v>4.018457271365603</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-0.07971544048932527</v>
+        <v>-0.07724971025312194</v>
       </c>
       <c r="E1880" t="n">
-        <v>3.125038191402055</v>
+        <v>3.126024483496536</v>
       </c>
       <c r="F1880" t="n">
-        <v>1.531917736343731</v>
+        <v>1.534383466579935</v>
       </c>
       <c r="G1880" t="n">
-        <v>4.076431433717771</v>
+        <v>4.077910871859493</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>0.0006569149746043501</v>
+        <v>0.003122645210807684</v>
       </c>
       <c r="E1881" t="n">
-        <v>3.171742354335143</v>
+        <v>3.172728646429625</v>
       </c>
       <c r="F1881" t="n">
-        <v>1.612290091807661</v>
+        <v>1.614755822043864</v>
       </c>
       <c r="G1881" t="n">
-        <v>4.139210067743646</v>
+        <v>4.140689505885367</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>0.03358878478745519</v>
+        <v>0.03605451502365853</v>
       </c>
       <c r="E1882" t="n">
-        <v>3.177695937358687</v>
+        <v>3.178682229453169</v>
       </c>
       <c r="F1882" t="n">
-        <v>1.612290091807661</v>
+        <v>1.614755822043864</v>
       </c>
       <c r="G1882" t="n">
-        <v>4.131990902842049</v>
+        <v>4.133470340983772</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>0.01342414323790786</v>
+        <v>0.01588987347411119</v>
       </c>
       <c r="E1883" t="n">
-        <v>3.162957889964892</v>
+        <v>3.163944182059374</v>
       </c>
       <c r="F1883" t="n">
-        <v>1.592125450258113</v>
+        <v>1.594591180494317</v>
       </c>
       <c r="G1883" t="n">
-        <v>4.113219927138345</v>
+        <v>4.114699365280067</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>0.07209107325944131</v>
+        <v>0.07455680349564464</v>
       </c>
       <c r="E1884" t="n">
-        <v>3.187540451812062</v>
+        <v>3.188526743906543</v>
       </c>
       <c r="F1884" t="n">
-        <v>1.677084918688251</v>
+        <v>1.679550648924454</v>
       </c>
       <c r="G1884" t="n">
-        <v>4.165311398034984</v>
+        <v>4.166790836176705</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>0.1351603055657808</v>
+        <v>0.1376260358019842</v>
       </c>
       <c r="E1885" t="n">
-        <v>3.215461873363713</v>
+        <v>3.216448165458194</v>
       </c>
       <c r="F1885" t="n">
-        <v>1.648571356006017</v>
+        <v>1.65103708624222</v>
       </c>
       <c r="G1885" t="n">
-        <v>4.150896989054758</v>
+        <v>4.152376427196479</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>0.1871758195345936</v>
+        <v>0.1896415497707969</v>
       </c>
       <c r="E1886" t="n">
-        <v>3.240258414637639</v>
+        <v>3.24124470673212</v>
       </c>
       <c r="F1886" t="n">
-        <v>1.648571356006017</v>
+        <v>1.65103708624222</v>
       </c>
       <c r="G1886" t="n">
-        <v>4.154887324741159</v>
+        <v>4.156366762882881</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>0.3627454884554975</v>
+        <v>0.3652112186917009</v>
       </c>
       <c r="E1887" t="n">
-        <v>3.309011055307258</v>
+        <v>3.30999734740174</v>
       </c>
       <c r="F1887" t="n">
-        <v>1.648571356006017</v>
+        <v>1.65103708624222</v>
       </c>
       <c r="G1887" t="n">
-        <v>4.153412097842417</v>
+        <v>4.154891535984139</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>0.5600148941834957</v>
+        <v>0.5624806244196989</v>
       </c>
       <c r="E1888" t="n">
-        <v>3.40297222776333</v>
+        <v>3.403958519857811</v>
       </c>
       <c r="F1888" t="n">
-        <v>1.845840761734015</v>
+        <v>1.848306491970218</v>
       </c>
       <c r="G1888" t="n">
-        <v>4.286827151444088</v>
+        <v>4.28830658958581</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>0.7643351654251821</v>
+        <v>0.7616327316567981</v>
       </c>
       <c r="E1889" t="n">
-        <v>3.471649202613321</v>
+        <v>3.470568229105968</v>
       </c>
       <c r="F1889" t="n">
-        <v>2.012297482681587</v>
+        <v>2.013629017920032</v>
       </c>
       <c r="G1889" t="n">
-        <v>4.373650050365948</v>
+        <v>4.374448971509015</v>
       </c>
     </row>
   </sheetData>
